--- a/TPE_25P822_N2.xlsx
+++ b/TPE_25P822_N2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="162">
   <si>
     <t xml:space="preserve">MATRICE DES RISQUES — Audit des Systèmes d'Information</t>
   </si>
@@ -342,129 +342,6 @@
   </si>
   <si>
     <t xml:space="preserve">Mettre à jour le registre. Réaliser une DPIA pour les nouveaux traitements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réseau &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable réseau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firewall Fortinet/Cisco / IDS-IPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des équipements réseau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configuration et supervision du pare-feu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIS Benchmarks / ISO 27001 A.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les règles du pare-feu sont-elles documentées, révisées périodiquement et conformes aux bonnes pratiques ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Règles pare-feu non auditées depuis 2 ans. Présence de règles permissives obsolètes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export des règles firewall, rapport d'audit de configuration, changelog des modifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intrusion réseau / Exposition de services internes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compromission du SI, espionnage industriel, ransomware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réaliser un audit de configuration firewall. Appliquer le moindre privilège réseau.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des tiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direction des Achats / DSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable des contrats IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acheteur IT / Juriste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outil GRC / SharePoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Évaluation et suivi des fournisseurs SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clauses de sécurité dans les contrats fournisseurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO 27001 A.15 / DORA (UE 2022/2554)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les contrats avec les prestataires SI incluent-ils des clauses de sécurité et de confidentialité ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certains contrats anciens ne contiennent pas de clauses RGPD ni de droit d'audit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contrats IT, avenant RGPD, résultats d'évaluation fournisseur, SLA de sécurité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Défaillance d'un prestataire / Fuite via un tiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupture de service, violation de données, responsabilité juridique partagée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mettre à jour les contrats. Intégrer systématiquement les clauses RGPD et droit d'audit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilisation &amp; Formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRH / RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable Formation / RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chargé de formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMS (Moodle / Docebo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programme de sensibilisation cybersécurité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existence d'un plan de formation annuel à la sécurité</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISO 27001 A.7 / Bonnes pratiques ANSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les collaborateurs bénéficient-ils d'une formation régulière aux risques cyber (phishing, mots de passe, etc.) ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aucune formation sécurité depuis 18 mois. Taux de clics phishing simulé : 34%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan de formation, attestations de suivi, résultats campagnes phishing, tableaux de bord formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erreur humaine / Ingénierie sociale réussie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compromission de comptes, ransomware via phishing, violation RGPD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lancer immédiatement une campagne de sensibilisation. Cible &lt; 5% sur phishing simulé.</t>
   </si>
   <si>
     <t xml:space="preserve">LÉGENDE — Criticité</t>
@@ -1471,156 +1348,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="N12" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="5">
@@ -1655,31 +1385,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1687,10 +1417,10 @@
         <v>63</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1698,51 +1428,51 @@
         <v>34</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1750,32 +1480,32 @@
         <v>7</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>172</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1783,76 +1513,76 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1860,10 +1590,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1871,10 +1601,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1882,7 +1612,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>34</v>
@@ -1893,10 +1623,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
